--- a/quizzes/005_sexual_cells_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/005_sexual_cells_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'mitosis'}</t>
+          <t>mitosis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Mitosis'}</t>
+          <t>Mitosis</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'meiosis'}</t>
+          <t>meiosis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Meiosis'}</t>
+          <t>Meiosis</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somatic'}</t>
+          <t>somatic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somatic'}</t>
+          <t>Somatic</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'plasma'}</t>
+          <t>plasma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Plasma'}</t>
+          <t>Plasma</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'cytoplasm'}</t>
+          <t>cytoplasm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Cytoplasm'}</t>
+          <t>Cytoplasm</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'nucleus'}</t>
+          <t>nucleus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Nucleus'}</t>
+          <t>Nucleus</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'diffusion'}</t>
+          <t>diffusion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Diffusion'}</t>
+          <t>Diffusion</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'osmosis'}</t>
+          <t>osmosis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Osmosis'}</t>
+          <t>Osmosis</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'endocytosis'}</t>
+          <t>endocytosis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Endocytosis'}</t>
+          <t>Endocytosis</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'exocytosis'}</t>
+          <t>exocytosis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Exocytosis'}</t>
+          <t>Exocytosis</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'mitosis'}</t>
+          <t>mitosis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Mitosis'}</t>
+          <t>Mitosis</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'meiosis'}</t>
+          <t>meiosis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Meiosis'}</t>
+          <t>Meiosis</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'apoptosis'}</t>
+          <t>apoptosis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Apoptosis'}</t>
+          <t>Apoptosis</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'necrosis'}</t>
+          <t>necrosis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Necrosis'}</t>
+          <t>Necrosis</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'g1'}</t>
+          <t>g1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'G1'}</t>
+          <t>G1</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'g2'}</t>
+          <t>g2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'G2'}</t>
+          <t>G2</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'s'}</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'S'}</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
